--- a/data/transit_time.xlsx
+++ b/data/transit_time.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrauniom\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C93211F-A3F6-4EF6-9737-FAAD7493730C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C6B4CF-2878-48CB-B232-A4957AC905CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>MUAC</t>
   </si>
@@ -89,9 +89,6 @@
     <t>HungaroControl</t>
   </si>
   <si>
-    <t>IAA</t>
-  </si>
-  <si>
     <t>LFV</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>SMATSA</t>
   </si>
   <si>
-    <t>UkSATSE</t>
-  </si>
-  <si>
     <t>BHANSA</t>
   </si>
   <si>
@@ -156,6 +150,9 @@
   </si>
   <si>
     <t>HASP</t>
+  </si>
+  <si>
+    <t>AirNav Ireland</t>
   </si>
 </sst>
 </file>
@@ -507,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -524,63 +521,63 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B8">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>21</v>
@@ -588,111 +585,111 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B18">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B19">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>11</v>
@@ -700,7 +697,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>16</v>
@@ -708,15 +705,15 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>10</v>
@@ -724,10 +721,10 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -740,7 +737,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29">
         <v>36</v>
@@ -748,7 +745,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>40</v>
@@ -756,7 +753,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>21</v>
@@ -764,7 +761,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>17</v>
@@ -772,15 +769,15 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34">
         <v>35</v>
@@ -788,31 +785,31 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38">
         <v>10</v>
@@ -820,23 +817,15 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B38">
-    <sortCondition ref="A2:A38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B38">
+    <sortCondition ref="A3:A38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -844,18 +833,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1082,6 +1071,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFC75A0-E02F-4958-BA20-E0643BE00BFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C121DFFC-1C78-46A8-AC2D-286473FD2932}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -1094,14 +1091,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
     <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFC75A0-E02F-4958-BA20-E0643BE00BFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1123,4 +1112,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/transit_time.xlsx
+++ b/data/transit_time.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrauniom\dev\repos\standard_inputs\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C6B4CF-2878-48CB-B232-A4957AC905CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF367D44-AE6B-4E70-B962-8064264AFE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -188,8 +188,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,304 +524,304 @@
       <c r="A2" t="s">
         <v>39</v>
       </c>
-      <c r="B2">
-        <v>30</v>
+      <c r="B2" s="1">
+        <v>30.342836701736932</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>12</v>
+      <c r="B3" s="1">
+        <v>11.944825204261152</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>19</v>
+      <c r="B4" s="1">
+        <v>18.992173944832359</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>14</v>
+      <c r="B5" s="1">
+        <v>13.780670905591551</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>18</v>
+      <c r="B6" s="1">
+        <v>18.106005438392362</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>37</v>
+      <c r="B7" s="1">
+        <v>37.485852119862699</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B8">
-        <v>13</v>
+      <c r="B8" s="1">
+        <v>13.239983672576241</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>21</v>
+      <c r="B9" s="1">
+        <v>20.885438978278128</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>21</v>
+      <c r="B10" s="1">
+        <v>20.992432533476503</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>29</v>
+      <c r="B11" s="1">
+        <v>28.695459450617005</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>29</v>
+      <c r="B12" s="1">
+        <v>29.346374880147621</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>59</v>
+      <c r="B13" s="1">
+        <v>59.081824944358182</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>44</v>
+      <c r="B14" s="1">
+        <v>44.112180731034954</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>20</v>
+      <c r="B15" s="1">
+        <v>20.38760466445504</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>47</v>
+      <c r="B16" s="1">
+        <v>47.032252813494601</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>40</v>
+      <c r="B17" s="1">
+        <v>39.805788267377579</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
-      <c r="B18">
-        <v>28</v>
+      <c r="B18" s="1">
+        <v>27.641342295867855</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
-      <c r="B19">
-        <v>44</v>
+      <c r="B19" s="1">
+        <v>43.180040586522701</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
-      <c r="B20">
-        <v>16</v>
+      <c r="B20" s="1">
+        <v>16.019432435274808</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
-      <c r="B21">
-        <v>36</v>
+      <c r="B21" s="1">
+        <v>35.516292407668651</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="B22">
-        <v>16</v>
+      <c r="B22" s="1">
+        <v>16.259198889323358</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23">
-        <v>11</v>
+      <c r="B23" s="1">
+        <v>10.65601181949318</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="B24">
-        <v>16</v>
+      <c r="B24" s="1">
+        <v>16.297829399892912</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25">
-        <v>37</v>
+      <c r="B25" s="1">
+        <v>36.970995385629536</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="B26">
-        <v>10</v>
+      <c r="B26" s="1">
+        <v>10.427217353798246</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
-      <c r="B27">
-        <v>13</v>
+      <c r="B27" s="1">
+        <v>13.288118872926814</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
-      <c r="B28">
-        <v>21</v>
+      <c r="B28" s="1">
+        <v>21.224131197662803</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
-      <c r="B29">
-        <v>36</v>
+      <c r="B29" s="1">
+        <v>36.295036142906348</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
-      <c r="B30">
-        <v>40</v>
+      <c r="B30" s="1">
+        <v>40.104205867690212</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
-      <c r="B31">
-        <v>21</v>
+      <c r="B31" s="1">
+        <v>20.552929900518887</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="B32">
-        <v>17</v>
+      <c r="B32" s="1">
+        <v>16.704190952576482</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="B33">
-        <v>34</v>
+      <c r="B33" s="1">
+        <v>33.877480933951318</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="B34">
-        <v>35</v>
+      <c r="B34" s="1">
+        <v>35.278849004420053</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B35">
-        <v>24</v>
+      <c r="B35" s="1">
+        <v>24.132552287670119</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
-      <c r="B36">
-        <v>10</v>
+      <c r="B36" s="1">
+        <v>10.462277462137388</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>33</v>
       </c>
-      <c r="B37">
-        <v>16</v>
+      <c r="B37" s="1">
+        <v>16.270143608241394</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>34</v>
       </c>
-      <c r="B38">
-        <v>10</v>
+      <c r="B38" s="1">
+        <v>10.000628496009051</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>35</v>
       </c>
-      <c r="B39">
-        <v>18</v>
+      <c r="B39" s="1">
+        <v>17.965645121851821</v>
       </c>
     </row>
   </sheetData>
@@ -833,21 +834,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7de07ceb4021a46e644f2475dce3c08e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a575a7fa9043b0502b32047f1ff6be7" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -1070,10 +1056,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFC75A0-E02F-4958-BA20-E0643BE00BFC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B74F9B-4F2C-4AA5-BDE5-CFDADF70D701}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1096,20 +1108,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B74F9B-4F2C-4AA5-BDE5-CFDADF70D701}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFC75A0-E02F-4958-BA20-E0643BE00BFC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/transit_time.xlsx
+++ b/data/transit_time.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C93211F-A3F6-4EF6-9737-FAAD7493730C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF367D44-AE6B-4E70-B962-8064264AFE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>MUAC</t>
   </si>
@@ -89,9 +89,6 @@
     <t>HungaroControl</t>
   </si>
   <si>
-    <t>IAA</t>
-  </si>
-  <si>
     <t>LFV</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>SMATSA</t>
   </si>
   <si>
-    <t>UkSATSE</t>
-  </si>
-  <si>
     <t>BHANSA</t>
   </si>
   <si>
@@ -156,6 +150,9 @@
   </si>
   <si>
     <t>HASP</t>
+  </si>
+  <si>
+    <t>AirNav Ireland</t>
   </si>
 </sst>
 </file>
@@ -191,8 +188,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -524,319 +522,311 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="B2" s="1">
+        <v>30.342836701736932</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>11.944825204261152</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>18.992173944832359</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
+        <v>13.780670905591551</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>18.106005438392362</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>37.485852119862699</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>21</v>
+        <v>36</v>
+      </c>
+      <c r="B8" s="1">
+        <v>13.239983672576241</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>20.885438978278128</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>20.992432533476503</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>28.695459450617005</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>59</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>29.346374880147621</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>59.081824944358182</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>44.112180731034954</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15">
-        <v>47</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>20.38760466445504</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>47.032252813494601</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>39.805788267377579</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="B18" s="1">
+        <v>27.641342295867855</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="B19" s="1">
+        <v>43.180040586522701</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>16.019432435274808</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>35.516292407668651</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>16.259198889323358</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>10.65601181949318</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>16.297829399892912</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>36</v>
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>36.970995385629536</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>10.427217353798246</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>13.288118872926814</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
-      <c r="B28">
-        <v>21</v>
+      <c r="B28" s="1">
+        <v>21.224131197662803</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="B29" s="1">
+        <v>36.295036142906348</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30">
-        <v>40</v>
+        <v>26</v>
+      </c>
+      <c r="B30" s="1">
+        <v>40.104205867690212</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="B31" s="1">
+        <v>20.552929900518887</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="B32" s="1">
+        <v>16.704190952576482</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33">
-        <v>35</v>
+        <v>29</v>
+      </c>
+      <c r="B33" s="1">
+        <v>33.877480933951318</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="B34" s="1">
+        <v>35.278849004420053</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="B35" s="1">
+        <v>24.132552287670119</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="B36" s="1">
+        <v>10.462277462137388</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="B37" s="1">
+        <v>16.270143608241394</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="B38" s="1">
+        <v>10.000628496009051</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="B39" s="1">
+        <v>17.965645121851821</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B38">
-    <sortCondition ref="A2:A38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B38">
+    <sortCondition ref="A3:A38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -844,21 +834,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100763DCA751E988E49B18D7A5F3E2E0A59" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7de07ceb4021a46e644f2475dce3c08e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd" xmlns:ns3="c78a888a-83d8-49bb-8890-6eb97e8a3c0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a575a7fa9043b0502b32047f1ff6be7" ns2:_="" ns3:_="">
     <xsd:import namespace="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
@@ -1081,7 +1056,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B74F9B-4F2C-4AA5-BDE5-CFDADF70D701}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
+    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C121DFFC-1C78-46A8-AC2D-286473FD2932}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -1098,7 +1107,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EFC75A0-E02F-4958-BA20-E0643BE00BFC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1106,21 +1115,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B74F9B-4F2C-4AA5-BDE5-CFDADF70D701}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="841a37d2-6ac6-4cb8-8211-c8824e7b4dcd"/>
-    <ds:schemaRef ds:uri="c78a888a-83d8-49bb-8890-6eb97e8a3c0e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>